--- a/Family pedigree.xlsx
+++ b/Family pedigree.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\family tree diagram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE29F84E-FAF8-4D5D-A9EB-65B77FD5859E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EF98DA-D93D-4341-8FFE-BD0391E1510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CFEAFA2F-0462-4EA1-9A29-A8B530A46476}"/>
   </bookViews>
@@ -535,7 +535,7 @@
       <c r="N4" t="s">
         <v>8</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="N5" t="s">
         <v>9</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>11</v>
       </c>
     </row>
